--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -591,7 +591,13 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFDiagnosticReportLabStatus</t>
+  </si>
+  <si>
+    <t>1489: terminologyMaps using VF_DiagnosticReportLabStatus on MICROBIOLOGY - PARASITE RPT STATUS (#63.05-15)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.ParasitologyReportStatus</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -607,12 +613,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1489: terminologyMaps using null on MICROBIOLOGY - PARASITE RPT STATUS (#63.05-15)</t>
-  </si>
-  <si>
-    <t>Micro.Microbiology.ParasitologyReportStatus</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -695,6 +695,9 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
+    <t>1528: fixed value = http://loinc.org#42807-8 Parasite identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -711,9 +714,6 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>1528: fixed value = http://loinc.org#42807-8 Parasite identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1814,7 +1814,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.65234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -1824,14 +1824,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2070,22 +2070,22 @@
         <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -2707,13 +2707,13 @@
         <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -2833,13 +2833,13 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -2959,13 +2959,13 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>84</v>
@@ -3087,13 +3087,13 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>84</v>
@@ -3204,25 +3204,25 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>84</v>
@@ -3330,22 +3330,22 @@
         <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3456,22 +3456,22 @@
         <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AP13" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -3597,13 +3597,13 @@
         <v>189</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>191</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -3717,16 +3717,16 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="AQ15" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -3847,16 +3847,16 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AQ16" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -3969,25 +3969,25 @@
         <v>216</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AP17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AQ17" t="s" s="2">
+      <c r="AR17" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AR17" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4094,25 +4094,25 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AO18" t="s" s="2">
+      <c r="AQ18" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>84</v>
@@ -4226,19 +4226,19 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AO19" t="s" s="2">
+      <c r="AQ19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4348,25 +4348,25 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4476,25 +4476,25 @@
         <v>258</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4608,19 +4608,19 @@
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4728,25 +4728,25 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4859,25 +4859,25 @@
         <v>84</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AO24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4988,16 +4988,16 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5113,25 +5113,25 @@
         <v>84</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5244,16 +5244,16 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5367,25 +5367,25 @@
         <v>84</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AO28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5498,16 +5498,16 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5621,25 +5621,25 @@
         <v>84</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AO30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5747,25 +5747,25 @@
         <v>84</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AO31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP31" t="s" s="2">
+      <c r="AQ31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR31" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR31" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5878,16 +5878,16 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6005,13 +6005,13 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6131,13 +6131,13 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6259,13 +6259,13 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6380,16 +6380,16 @@
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6504,16 +6504,16 @@
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6629,19 +6629,19 @@
         <v>84</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6757,19 +6757,19 @@
         <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6889,13 +6889,13 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7010,16 +7010,16 @@
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7136,16 +7136,16 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7262,16 +7262,16 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7390,16 +7390,16 @@
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7517,13 +7517,13 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7643,13 +7643,13 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7771,13 +7771,13 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -7893,22 +7893,22 @@
         <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AM48" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AP48" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ48" t="s" s="2">
-        <v>84</v>
+        <v>221</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8021,25 +8021,25 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
+      <c r="AQ49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -8152,16 +8152,16 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8277,25 +8277,25 @@
         <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP51" t="s" s="2">
+      <c r="AQ51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -8408,16 +8408,16 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,10 +591,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFDiagnosticReportLabStatus</t>
-  </si>
-  <si>
-    <t>1489: terminologyMaps using VF_DiagnosticReportLabStatus on MICROBIOLOGY - PARASITE RPT STATUS (#63.05-15)</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
+  </si>
+  <si>
+    <t>1489: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - PARASITE RPT STATUS (#63.05-15)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ParasitologyReportStatus</t>
@@ -1814,7 +1814,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.65234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="553">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,6 +515,209 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>Observation.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Observation.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Observation.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>Observation.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>1476: source value from MICROBIOLOGY - IEN (#63.05-.001)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>Observation.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>Observation.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
     <t>Observation.basedOn</t>
   </si>
   <si>
@@ -588,9 +791,6 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
   </si>
   <si>
@@ -618,10 +818,6 @@
     <t>Observation.category</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Classification of  type of observation</t>
   </si>
   <si>
@@ -632,31 +828,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -667,6 +838,31 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
+  </si>
+  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -686,9 +882,6 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>LOINC codes</t>
   </si>
   <si>
@@ -714,6 +907,67 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case Not NULL</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -735,6 +989,12 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -824,6 +1084,10 @@
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">us-core-1
 </t>
   </si>
@@ -844,6 +1108,22 @@
     <t>FiveWs.done[x]</t>
   </si>
   <si>
+    <t>Observation.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (#63.05-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime</t>
+  </si>
+  <si>
     <t>Observation.issued</t>
   </si>
   <si>
@@ -860,6 +1140,12 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
+    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (#63.05-.03)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.ReportCompletedDateTime</t>
+  </si>
+  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -885,6 +1171,9 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (#63.05-.04)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1018,6 +1307,12 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
+    <t>1455: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - COMMENT &gt; COMMENT - COMMENT (#63.05-12 &gt; 63.3-2 &gt; 63.31-.01)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.SpecimenComment</t>
+  </si>
+  <si>
     <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
   </si>
   <si>
@@ -1101,6 +1396,12 @@
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
   </si>
   <si>
+    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (#63.05-.06)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.MicrobiologyAccession</t>
+  </si>
+  <si>
     <t>&lt; 123038009 |Specimen|</t>
   </si>
   <si>
@@ -1173,29 +1474,7 @@
     <t>Observation.referenceRange.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.referenceRange.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -1786,12 +2065,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR52"/>
+  <dimension ref="A1:AR65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1808,16 +2087,16 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="50.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
@@ -1825,7 +2104,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
@@ -3237,14 +3516,14 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>84</v>
@@ -3253,21 +3532,19 @@
         <v>84</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>165</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>84</v>
       </c>
@@ -3315,19 +3592,19 @@
         <v>84</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>84</v>
@@ -3336,16 +3613,16 @@
         <v>84</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3356,14 +3633,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3379,19 +3656,19 @@
         <v>84</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3429,19 +3706,19 @@
         <v>84</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>82</v>
@@ -3453,7 +3730,7 @@
         <v>84</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>84</v>
@@ -3462,16 +3739,16 @@
         <v>84</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>84</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -3482,10 +3759,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3493,13 +3770,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>95</v>
@@ -3511,16 +3788,16 @@
         <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>84</v>
@@ -3545,11 +3822,13 @@
         <v>84</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>84</v>
@@ -3567,10 +3846,10 @@
         <v>84</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>94</v>
@@ -3582,25 +3861,25 @@
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>84</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>84</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>189</v>
+        <v>137</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>191</v>
+        <v>84</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>84</v>
@@ -3608,10 +3887,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3619,34 +3898,34 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G15" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K15" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>84</v>
@@ -3671,35 +3950,37 @@
         <v>84</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>84</v>
@@ -3720,13 +4001,13 @@
         <v>84</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -3734,35 +4015,33 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>194</v>
@@ -3784,10 +4063,10 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>206</v>
+        <v>84</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>84</v>
@@ -3799,37 +4078,37 @@
         <v>84</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>84</v>
       </c>
       <c r="Z16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>192</v>
-      </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>84</v>
@@ -3850,13 +4129,13 @@
         <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -3864,18 +4143,18 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>94</v>
@@ -3890,20 +4169,18 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>84</v>
       </c>
@@ -3915,7 +4192,7 @@
         <v>84</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>84</v>
@@ -3927,13 +4204,13 @@
         <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>84</v>
@@ -3954,7 +4231,7 @@
         <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>94</v>
@@ -3966,36 +4243,36 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>217</v>
+        <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>221</v>
+        <v>84</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>222</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4003,13 +4280,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>84</v>
@@ -4018,20 +4295,16 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>84</v>
       </c>
@@ -4079,7 +4352,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4100,19 +4373,19 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>232</v>
+        <v>84</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>84</v>
@@ -4120,10 +4393,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4134,7 +4407,7 @@
         <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>84</v>
@@ -4146,16 +4419,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4205,13 +4478,13 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>84</v>
@@ -4232,13 +4505,13 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>232</v>
+        <v>84</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4246,21 +4519,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>84</v>
@@ -4272,19 +4545,17 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4333,13 +4604,13 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>84</v>
@@ -4354,19 +4625,19 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>249</v>
+        <v>84</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4374,24 +4645,24 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>84</v>
@@ -4400,20 +4671,18 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>84</v>
       </c>
@@ -4461,19 +4730,19 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>257</v>
+        <v>84</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>258</v>
+        <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>84</v>
@@ -4482,19 +4751,19 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>262</v>
+        <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4502,10 +4771,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4513,33 +4782,35 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>264</v>
+        <v>114</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
       </c>
@@ -4563,13 +4834,11 @@
         <v>84</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>84</v>
+        <v>249</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>84</v>
@@ -4587,10 +4856,10 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>94</v>
@@ -4602,25 +4871,25 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>84</v>
+        <v>250</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>84</v>
+        <v>251</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>84</v>
+        <v>252</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>84</v>
+        <v>253</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4628,10 +4897,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4639,32 +4908,34 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>183</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O23" t="s" s="2">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4674,7 +4945,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -4689,31 +4960,29 @@
         <v>84</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4728,25 +4997,25 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>266</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>276</v>
+        <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>277</v>
+        <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4754,18 +5023,20 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
@@ -4777,22 +5048,22 @@
         <v>84</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>281</v>
+        <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -4802,7 +5073,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -4817,13 +5088,13 @@
         <v>84</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -4841,19 +5112,19 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>286</v>
+        <v>84</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>287</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>84</v>
@@ -4865,35 +5136,35 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>288</v>
+        <v>84</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>289</v>
+        <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>84</v>
+        <v>268</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>291</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>84</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>94</v>
@@ -4905,22 +5176,22 @@
         <v>84</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -4945,11 +5216,13 @@
         <v>84</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -4967,62 +5240,62 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>84</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>137</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>84</v>
+        <v>284</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>84</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>84</v>
@@ -5034,20 +5307,16 @@
         <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>302</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>84</v>
       </c>
@@ -5071,13 +5340,13 @@
         <v>84</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>306</v>
+        <v>84</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>307</v>
+        <v>84</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>84</v>
@@ -5095,19 +5364,19 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>300</v>
+        <v>164</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>84</v>
@@ -5119,31 +5388,31 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>308</v>
+        <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>309</v>
+        <v>84</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>310</v>
+        <v>165</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>311</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5162,20 +5431,18 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>313</v>
+        <v>140</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>314</v>
+        <v>141</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>315</v>
+        <v>167</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>84</v>
       </c>
@@ -5211,19 +5478,19 @@
         <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>312</v>
+        <v>171</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5235,7 +5502,7 @@
         <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>84</v>
@@ -5250,10 +5517,10 @@
         <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>318</v>
+        <v>84</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>319</v>
+        <v>165</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5264,10 +5531,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5278,30 +5545,32 @@
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>193</v>
+        <v>289</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
       </c>
@@ -5325,13 +5594,13 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>324</v>
+        <v>84</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>325</v>
+        <v>84</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>326</v>
+        <v>84</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -5349,13 +5618,13 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>84</v>
@@ -5364,7 +5633,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5373,27 +5642,27 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>327</v>
+        <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>330</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5413,22 +5682,22 @@
         <v>84</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5453,13 +5722,13 @@
         <v>84</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>324</v>
+        <v>84</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>337</v>
+        <v>84</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
@@ -5477,7 +5746,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5504,10 +5773,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5518,10 +5787,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5529,33 +5798,35 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>341</v>
+        <v>307</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>343</v>
+        <v>309</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -5603,7 +5874,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5618,36 +5889,36 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>84</v>
+        <v>314</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>346</v>
+        <v>315</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>347</v>
+        <v>316</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>84</v>
+        <v>317</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>348</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>349</v>
+        <v>318</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>349</v>
+        <v>318</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5658,7 +5929,7 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>84</v>
@@ -5667,19 +5938,19 @@
         <v>84</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>351</v>
+        <v>320</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5729,13 +6000,13 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>349</v>
+        <v>318</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
@@ -5753,38 +6024,38 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>354</v>
+        <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>355</v>
+        <v>282</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>317</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>357</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>358</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>358</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>84</v>
+        <v>325</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>84</v>
@@ -5793,22 +6064,22 @@
         <v>84</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>359</v>
+        <v>326</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>360</v>
+        <v>327</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>361</v>
+        <v>328</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>362</v>
+        <v>329</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>363</v>
+        <v>330</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -5857,19 +6128,19 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>358</v>
+        <v>324</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>364</v>
+        <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>84</v>
@@ -5878,19 +6149,19 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>84</v>
+        <v>331</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>365</v>
+        <v>332</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>334</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -5898,14 +6169,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5915,25 +6186,29 @@
         <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>368</v>
+        <v>337</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>369</v>
+        <v>338</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
       </c>
@@ -5969,19 +6244,17 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>371</v>
+        <v>335</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -5990,10 +6263,10 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
@@ -6002,19 +6275,19 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>84</v>
+        <v>346</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>84</v>
+        <v>348</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6022,44 +6295,48 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="D34" t="s" s="2">
-        <v>139</v>
+        <v>336</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>140</v>
+        <v>351</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>141</v>
+        <v>338</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>374</v>
+        <v>339</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
       </c>
@@ -6107,40 +6384,40 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>375</v>
+        <v>335</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>145</v>
+        <v>344</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>352</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>84</v>
+        <v>353</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>84</v>
+        <v>346</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
+        <v>348</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -6148,46 +6425,44 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>377</v>
+        <v>84</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>140</v>
+        <v>355</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
@@ -6235,25 +6510,25 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>84</v>
+        <v>360</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>84</v>
@@ -6262,13 +6537,13 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>84</v>
+        <v>361</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>137</v>
+        <v>362</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>84</v>
+        <v>363</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6276,10 +6551,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6290,28 +6565,30 @@
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
       </c>
@@ -6359,40 +6636,40 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>385</v>
+        <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>84</v>
+        <v>370</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
+        <v>373</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6400,10 +6677,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6417,25 +6694,29 @@
         <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
       </c>
@@ -6483,7 +6764,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6492,42 +6773,42 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6541,7 +6822,7 @@
         <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>84</v>
@@ -6550,19 +6831,19 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6587,13 +6868,11 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6611,7 +6890,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6620,7 +6899,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>84</v>
+        <v>392</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6635,13 +6914,13 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>399</v>
+        <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>400</v>
+        <v>137</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>310</v>
+        <v>393</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6652,14 +6931,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>84</v>
+        <v>395</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6678,19 +6957,19 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6715,13 +6994,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>324</v>
+        <v>188</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -6739,7 +7018,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6763,27 +7042,27 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>310</v>
+        <v>404</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>84</v>
+        <v>405</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6794,10 +7073,10 @@
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>84</v>
@@ -6806,17 +7085,19 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -6865,13 +7146,13 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>84</v>
@@ -6880,10 +7161,10 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>84</v>
+        <v>412</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>84</v>
+        <v>413</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>84</v>
@@ -6892,10 +7173,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>84</v>
+        <v>414</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -6906,10 +7187,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6932,15 +7213,17 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>368</v>
+        <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -6965,13 +7248,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>84</v>
+        <v>421</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>84</v>
+        <v>422</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -6989,7 +7272,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7013,27 +7296,27 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>84</v>
+        <v>423</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>84</v>
+        <v>426</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7044,7 +7327,7 @@
         <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>84</v>
@@ -7053,21 +7336,23 @@
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>419</v>
+        <v>183</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7091,13 +7376,13 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>84</v>
+        <v>432</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>84</v>
+        <v>433</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7115,13 +7400,13 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>84</v>
@@ -7142,10 +7427,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7156,10 +7441,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7170,28 +7455,28 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7241,13 +7526,13 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
@@ -7256,36 +7541,36 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>84</v>
+        <v>441</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>84</v>
+        <v>442</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>84</v>
+        <v>443</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>84</v>
+        <v>446</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7296,7 +7581,7 @@
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>84</v>
@@ -7305,23 +7590,21 @@
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>359</v>
+        <v>448</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7369,13 +7652,13 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>84</v>
@@ -7393,27 +7676,27 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>84</v>
+        <v>452</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7424,7 +7707,7 @@
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>84</v>
@@ -7436,16 +7719,20 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>368</v>
+        <v>457</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>458</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7493,19 +7780,19 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>371</v>
+        <v>456</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -7520,10 +7807,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>372</v>
+        <v>464</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7534,21 +7821,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>84</v>
@@ -7560,17 +7847,15 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7619,19 +7904,19 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>375</v>
+        <v>164</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>84</v>
@@ -7649,7 +7934,7 @@
         <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>372</v>
+        <v>165</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7660,14 +7945,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>377</v>
+        <v>139</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7680,26 +7965,24 @@
         <v>84</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>378</v>
+        <v>141</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>167</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O47" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -7747,7 +8030,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>171</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7777,7 +8060,7 @@
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -7788,45 +8071,45 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>443</v>
+        <v>470</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>444</v>
+        <v>143</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>212</v>
+        <v>149</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -7851,13 +8134,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>324</v>
+        <v>84</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>445</v>
+        <v>84</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -7875,19 +8158,19 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>441</v>
+        <v>471</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>84</v>
@@ -7899,16 +8182,16 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>446</v>
+        <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>219</v>
+        <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>221</v>
+        <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -7916,10 +8199,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7939,23 +8222,19 @@
         <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>281</v>
+        <v>473</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8003,7 +8282,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8012,7 +8291,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>84</v>
+        <v>476</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8027,27 +8306,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>451</v>
+        <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>289</v>
+        <v>477</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>290</v>
+        <v>478</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>291</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8070,20 +8349,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>193</v>
+        <v>473</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8107,13 +8382,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>456</v>
+        <v>84</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>297</v>
+        <v>84</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8131,7 +8406,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8140,7 +8415,7 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8158,10 +8433,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>137</v>
+        <v>477</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>299</v>
+        <v>482</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8172,21 +8447,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
@@ -8198,19 +8473,19 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>302</v>
+        <v>484</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>303</v>
+        <v>485</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>304</v>
+        <v>486</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>305</v>
+        <v>487</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8235,13 +8510,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>213</v>
+        <v>118</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>306</v>
+        <v>488</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>307</v>
+        <v>489</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8259,13 +8534,13 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>84</v>
@@ -8283,27 +8558,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>308</v>
+        <v>490</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>309</v>
+        <v>491</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>310</v>
+        <v>404</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>311</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8326,19 +8601,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>493</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
+        <v>494</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>362</v>
+        <v>495</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>363</v>
+        <v>496</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8363,13 +8638,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>84</v>
+        <v>497</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>84</v>
+        <v>498</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8387,7 +8662,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8411,23 +8686,1671 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>84</v>
+        <v>490</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>365</v>
+        <v>491</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR53" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR54" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR55" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR56" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR57" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR58" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR59" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR60" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AR61" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR62" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR63" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR64" t="s" s="2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR65" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR52">
+  <autoFilter ref="A1:AR65">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8437,7 +10360,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI51">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -662,7 +662,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1476: source value from MICROBIOLOGY - IEN (#63.05-.001)</t>
+    <t>1476: source value from MICROBIOLOGY - IEN (63.05-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -794,7 +794,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
   </si>
   <si>
-    <t>1489: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - PARASITE RPT STATUS (#63.05-15)</t>
+    <t>1489: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - PARASITE RPT STATUS (63.05-15)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ParasitologyReportStatus</t>
@@ -888,7 +888,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
-    <t>1528: fixed value = http://loinc.org#42807-8 Parasite identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
+    <t>1528: fixed value = http://loinc.org#42807-8 Parasite identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case NULL</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -937,7 +937,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case Not NULL</t>
+    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case Not NULL</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
@@ -989,7 +989,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
@@ -1118,7 +1118,7 @@
 </t>
   </si>
   <si>
-    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (#63.05-.01)</t>
+    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime</t>
@@ -1140,7 +1140,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (#63.05-.03)</t>
+    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
@@ -1171,7 +1171,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (#63.05-.04)</t>
+    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1307,7 +1307,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>1455: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - COMMENT &gt; COMMENT - COMMENT (#63.05-12 &gt; 63.3-2 &gt; 63.31-.01)</t>
+    <t>1455: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - COMMENT &gt; COMMENT - COMMENT (63.05-12 &gt; 63.3-2 &gt; 63.31-.01)</t>
   </si>
   <si>
     <t>Micro.Microbiology.SpecimenComment</t>
@@ -1396,7 +1396,7 @@
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
   </si>
   <si>
-    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (#63.05-.06)</t>
+    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (63.05-.06)</t>
   </si>
   <si>
     <t>Micro.Microbiology.MicrobiologyAccession</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="554">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -992,7 +992,7 @@
     <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1121,7 +1121,7 @@
     <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime</t>
+    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1172,6 +1172,9 @@
   </si>
   <si>
     <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -6654,22 +6657,22 @@
         <v>369</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>84</v>
+        <v>370</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6677,10 +6680,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6703,19 +6706,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6764,7 +6767,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6773,10 +6776,10 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -6788,27 +6791,27 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6834,16 +6837,16 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6872,7 +6875,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6890,7 +6893,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6899,7 +6902,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6920,7 +6923,7 @@
         <v>137</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6931,14 +6934,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6960,16 +6963,16 @@
         <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6997,10 +7000,10 @@
         <v>188</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7018,7 +7021,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7042,27 +7045,27 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7085,19 +7088,19 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7146,7 +7149,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7161,10 +7164,10 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>84</v>
@@ -7173,10 +7176,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7187,10 +7190,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7216,13 +7219,13 @@
         <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7248,13 +7251,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7272,7 +7275,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7296,27 +7299,27 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7342,16 +7345,16 @@
         <v>183</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
@@ -7376,13 +7379,13 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7400,7 +7403,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7427,10 +7430,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7441,10 +7444,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7467,16 +7470,16 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7526,7 +7529,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7541,36 +7544,36 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7593,16 +7596,16 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7652,7 +7655,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7676,27 +7679,27 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7719,19 +7722,19 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7780,7 +7783,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7792,7 +7795,7 @@
         <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -7807,10 +7810,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7821,10 +7824,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7945,10 +7948,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8071,14 +8074,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8100,10 +8103,10 @@
         <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>143</v>
@@ -8158,7 +8161,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8199,10 +8202,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8225,13 +8228,13 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8282,7 +8285,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8291,7 +8294,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8309,10 +8312,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8323,10 +8326,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8349,13 +8352,13 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8406,7 +8409,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8415,7 +8418,7 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8433,10 +8436,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8447,10 +8450,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8476,16 +8479,16 @@
         <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8513,10 +8516,10 @@
         <v>118</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8534,7 +8537,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8558,13 +8561,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8575,10 +8578,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8604,16 +8607,16 @@
         <v>183</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8638,13 +8641,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8662,7 +8665,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8686,13 +8689,13 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8703,10 +8706,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8729,17 +8732,17 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8788,7 +8791,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8818,7 +8821,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8829,10 +8832,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8858,10 +8861,10 @@
         <v>161</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8912,7 +8915,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8939,10 +8942,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8953,10 +8956,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8979,16 +8982,16 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9038,7 +9041,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9065,10 +9068,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9079,10 +9082,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9105,16 +9108,16 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9164,7 +9167,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9191,10 +9194,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9205,10 +9208,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9231,19 +9234,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9292,7 +9295,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9319,10 +9322,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9333,10 +9336,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9457,10 +9460,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9583,14 +9586,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9612,10 +9615,10 @@
         <v>140</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>143</v>
@@ -9670,7 +9673,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9711,10 +9714,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9740,13 +9743,13 @@
         <v>183</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>276</v>
@@ -9774,10 +9777,10 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>278</v>
@@ -9798,7 +9801,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>94</v>
@@ -9822,7 +9825,7 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>282</v>
@@ -9839,10 +9842,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9865,19 +9868,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9926,7 +9929,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9950,27 +9953,27 @@
         <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9996,16 +9999,16 @@
         <v>183</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10033,10 +10036,10 @@
         <v>188</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -10054,7 +10057,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10063,7 +10066,7 @@
         <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -10084,7 +10087,7 @@
         <v>137</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10095,14 +10098,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10124,16 +10127,16 @@
         <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10161,10 +10164,10 @@
         <v>188</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10182,7 +10185,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10206,27 +10209,27 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10252,16 +10255,16 @@
         <v>85</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10310,7 +10313,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10337,10 +10340,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$72</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="599">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,10 +632,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>1476-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -944,6 +950,136 @@
   </si>
   <si>
     <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1480-1: fixed value = http://loinc.org case Not NULL</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>1480-2: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) case Not NULL</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>1480-3: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) case Not NULL</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -2068,7 +2204,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR65"/>
+  <dimension ref="A1:AR72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -4035,7 +4171,7 @@
         <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>84</v>
@@ -4066,10 +4202,10 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>84</v>
@@ -4105,7 +4241,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4120,7 +4256,7 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -4132,10 +4268,10 @@
         <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4146,10 +4282,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4175,13 +4311,13 @@
         <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4195,7 +4331,7 @@
         <v>84</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>84</v>
@@ -4231,7 +4367,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4246,7 +4382,7 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
@@ -4258,10 +4394,10 @@
         <v>84</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
@@ -4272,10 +4408,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4298,13 +4434,13 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4355,7 +4491,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4382,10 +4518,10 @@
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4396,10 +4532,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4422,16 +4558,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4481,7 +4617,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4508,10 +4644,10 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4522,14 +4658,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4548,17 +4684,17 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4607,7 +4743,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4628,16 +4764,16 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4648,14 +4784,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4674,16 +4810,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4733,7 +4869,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4754,16 +4890,16 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -4774,10 +4910,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4803,16 +4939,16 @@
         <v>114</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
@@ -4841,7 +4977,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>84</v>
@@ -4859,7 +4995,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>94</v>
@@ -4874,25 +5010,25 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4900,10 +5036,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4929,16 +5065,16 @@
         <v>183</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4948,7 +5084,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -4966,16 +5102,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4985,7 +5121,7 @@
         <v>170</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5000,7 +5136,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -5015,10 +5151,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5026,13 +5162,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5057,16 +5193,16 @@
         <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5076,7 +5212,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5094,10 +5230,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5115,7 +5251,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5145,10 +5281,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5156,14 +5292,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5185,16 +5321,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5222,10 +5358,10 @@
         <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5243,7 +5379,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5258,36 +5394,36 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5408,10 +5544,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5534,10 +5670,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5560,19 +5696,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5621,7 +5757,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5636,7 +5772,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5648,10 +5784,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5662,10 +5798,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5685,23 +5821,19 @@
         <v>84</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>299</v>
+        <v>162</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>84</v>
       </c>
@@ -5749,7 +5881,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>303</v>
+        <v>164</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5761,7 +5893,7 @@
         <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>84</v>
@@ -5776,10 +5908,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>305</v>
+        <v>165</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5790,46 +5922,44 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>307</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>308</v>
+        <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>309</v>
+        <v>167</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -5865,52 +5995,52 @@
         <v>84</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>171</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>313</v>
+        <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>314</v>
+        <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>315</v>
+        <v>84</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>316</v>
+        <v>165</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>317</v>
+        <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -5918,10 +6048,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5932,10 +6062,10 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -5944,18 +6074,20 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>319</v>
+        <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -6003,13 +6135,13 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
@@ -6018,7 +6150,7 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>84</v>
+        <v>308</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -6030,13 +6162,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>317</v>
+        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6044,14 +6176,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>325</v>
+        <v>84</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6070,20 +6202,18 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>326</v>
+        <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>84</v>
       </c>
@@ -6131,7 +6261,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6152,19 +6282,19 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>331</v>
+        <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6172,14 +6302,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6198,19 +6328,17 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>337</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6247,17 +6375,19 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6266,31 +6396,31 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>344</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>323</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>348</v>
+        <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6298,16 +6428,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6326,19 +6454,17 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>351</v>
+        <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6387,7 +6513,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6396,31 +6522,31 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>344</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>353</v>
+        <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>348</v>
+        <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -6428,10 +6554,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6445,7 +6571,7 @@
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>84</v>
@@ -6454,18 +6580,20 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
@@ -6513,7 +6641,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6528,10 +6656,10 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>359</v>
+        <v>84</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>360</v>
+        <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>84</v>
@@ -6540,13 +6668,13 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>363</v>
+        <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6554,10 +6682,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6568,10 +6696,10 @@
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
@@ -6580,17 +6708,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>365</v>
+        <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6639,13 +6769,13 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>84</v>
@@ -6654,25 +6784,25 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>369</v>
+        <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>371</v>
+        <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6680,10 +6810,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6691,7 +6821,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>94</v>
@@ -6706,19 +6836,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6767,7 +6897,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6776,42 +6906,42 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>382</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>84</v>
+        <v>358</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6822,32 +6952,30 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>183</v>
+        <v>364</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
@@ -6871,11 +6999,13 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>392</v>
+        <v>84</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6893,16 +7023,16 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>393</v>
+        <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6920,13 +7050,13 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>137</v>
+        <v>284</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -6934,21 +7064,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>84</v>
@@ -6957,22 +7087,22 @@
         <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>183</v>
+        <v>371</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6997,13 +7127,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>402</v>
+        <v>84</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7021,13 +7151,13 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>84</v>
@@ -7042,41 +7172,41 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>403</v>
+        <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>405</v>
+        <v>378</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>84</v>
+        <v>379</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>406</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>407</v>
+        <v>380</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>407</v>
+        <v>380</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>95</v>
@@ -7085,22 +7215,22 @@
         <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>409</v>
+        <v>383</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7137,52 +7267,50 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>407</v>
+        <v>380</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>413</v>
+        <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>84</v>
+        <v>393</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7190,14 +7318,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="D41" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7207,27 +7337,29 @@
         <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>183</v>
+        <v>396</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>418</v>
+        <v>383</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>419</v>
+        <v>384</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
       </c>
@@ -7251,13 +7383,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>421</v>
+        <v>84</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>422</v>
+        <v>84</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7275,7 +7407,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>417</v>
+        <v>380</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7284,42 +7416,42 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>397</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>424</v>
+        <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>426</v>
+        <v>392</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>84</v>
+        <v>393</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>427</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>428</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>428</v>
+        <v>399</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7333,29 +7465,27 @@
         <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>183</v>
+        <v>400</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7379,13 +7509,13 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>421</v>
+        <v>84</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>433</v>
+        <v>84</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>434</v>
+        <v>84</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7403,7 +7533,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>428</v>
+        <v>399</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7418,10 +7548,10 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>84</v>
+        <v>404</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>84</v>
@@ -7430,13 +7560,13 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>435</v>
+        <v>406</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>436</v>
+        <v>407</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>84</v>
+        <v>408</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7444,10 +7574,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7458,7 +7588,7 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>95</v>
@@ -7467,21 +7597,21 @@
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>438</v>
+        <v>410</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>439</v>
+        <v>411</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7529,13 +7659,13 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
@@ -7544,36 +7674,36 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>442</v>
+        <v>414</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>84</v>
+        <v>416</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>444</v>
+        <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>446</v>
+        <v>418</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>419</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>447</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7587,27 +7717,29 @@
         <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>449</v>
+        <v>421</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>451</v>
+        <v>423</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7655,7 +7787,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7664,10 +7796,10 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>84</v>
+        <v>426</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>427</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7679,27 +7811,27 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>456</v>
+        <v>431</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7710,10 +7842,10 @@
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>84</v>
@@ -7722,19 +7854,19 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>458</v>
+        <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7759,13 +7891,11 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>84</v>
+        <v>437</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7783,19 +7913,19 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>463</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -7810,10 +7940,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>464</v>
+        <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7824,21 +7954,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>84</v>
+        <v>441</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>84</v>
@@ -7850,16 +7980,20 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>162</v>
+        <v>442</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -7883,13 +8017,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>84</v>
+        <v>447</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -7907,19 +8041,19 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>164</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>84</v>
@@ -7931,31 +8065,31 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>84</v>
+        <v>448</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>84</v>
+        <v>449</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>165</v>
+        <v>450</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>84</v>
+        <v>451</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7965,7 +8099,7 @@
         <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>84</v>
@@ -7974,18 +8108,20 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>453</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>141</v>
+        <v>454</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>167</v>
+        <v>455</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8033,7 +8169,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>171</v>
+        <v>452</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8045,13 +8181,13 @@
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>84</v>
+        <v>458</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>84</v>
+        <v>459</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
@@ -8060,10 +8196,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>84</v>
+        <v>460</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>165</v>
+        <v>461</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8074,46 +8210,44 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>469</v>
+        <v>84</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8137,13 +8271,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>84</v>
+        <v>466</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>84</v>
+        <v>467</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8161,43 +8295,43 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8228,16 +8362,20 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8261,13 +8399,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>84</v>
+        <v>466</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>84</v>
+        <v>478</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>84</v>
+        <v>479</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8294,7 +8432,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>477</v>
+        <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8312,10 +8450,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8326,10 +8464,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8343,7 +8481,7 @@
         <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>84</v>
@@ -8352,15 +8490,17 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>485</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8409,7 +8549,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8418,42 +8558,42 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>477</v>
+        <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>84</v>
+        <v>487</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>84</v>
+        <v>488</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>84</v>
+        <v>489</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>84</v>
+        <v>492</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8476,20 +8616,18 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>183</v>
+        <v>494</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8513,13 +8651,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>489</v>
+        <v>84</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>490</v>
+        <v>84</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8537,7 +8675,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8561,27 +8699,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>405</v>
+        <v>500</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>84</v>
+        <v>501</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8604,19 +8742,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>183</v>
+        <v>503</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8641,13 +8779,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>421</v>
+        <v>84</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>498</v>
+        <v>84</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>499</v>
+        <v>84</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8665,7 +8803,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8677,7 +8815,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>508</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8689,13 +8827,13 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>491</v>
+        <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>405</v>
+        <v>510</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8706,10 +8844,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8732,18 +8870,16 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>501</v>
+        <v>161</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>502</v>
+        <v>162</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>503</v>
+        <v>163</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>504</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -8791,7 +8927,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>500</v>
+        <v>164</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8803,7 +8939,7 @@
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8821,7 +8957,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>505</v>
+        <v>165</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8832,21 +8968,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>84</v>
@@ -8858,15 +8994,17 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>507</v>
+        <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -8915,19 +9053,19 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>506</v>
+        <v>171</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -8942,10 +9080,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>478</v>
+        <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>509</v>
+        <v>165</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8956,14 +9094,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>84</v>
+        <v>514</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8976,24 +9114,26 @@
         <v>84</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>511</v>
+        <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
@@ -9041,7 +9181,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9053,7 +9193,7 @@
         <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>84</v>
@@ -9068,10 +9208,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>515</v>
+        <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>516</v>
+        <v>137</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9082,10 +9222,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9096,7 +9236,7 @@
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>84</v>
@@ -9105,20 +9245,18 @@
         <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N56" t="s" s="2">
         <v>521</v>
       </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9167,16 +9305,16 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9194,10 +9332,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9208,10 +9346,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9222,7 +9360,7 @@
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -9231,23 +9369,19 @@
         <v>84</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>458</v>
+        <v>519</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O57" t="s" s="2">
         <v>527</v>
       </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9295,16 +9429,16 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9322,10 +9456,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9336,10 +9470,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9362,16 +9496,20 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>162</v>
+        <v>530</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9395,13 +9533,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>84</v>
+        <v>534</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>84</v>
+        <v>535</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9419,7 +9557,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>164</v>
+        <v>529</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9431,7 +9569,7 @@
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9443,13 +9581,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>84</v>
+        <v>536</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>84</v>
+        <v>537</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>165</v>
+        <v>450</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9460,14 +9598,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9486,18 +9624,20 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>141</v>
+        <v>539</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>167</v>
+        <v>540</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9521,13 +9661,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>84</v>
+        <v>466</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>84</v>
+        <v>543</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>84</v>
+        <v>544</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9545,7 +9685,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>171</v>
+        <v>538</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9557,7 +9697,7 @@
         <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -9569,13 +9709,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>84</v>
+        <v>536</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>84</v>
+        <v>537</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>165</v>
+        <v>450</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9586,45 +9726,43 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>469</v>
+        <v>84</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>140</v>
+        <v>546</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>470</v>
+        <v>547</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>149</v>
+        <v>549</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9673,19 +9811,19 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>472</v>
+        <v>545</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -9703,7 +9841,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>137</v>
+        <v>550</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9714,10 +9852,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9725,7 +9863,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>94</v>
@@ -9737,23 +9875,19 @@
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -9777,13 +9911,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>421</v>
+        <v>84</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>537</v>
+        <v>84</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9801,10 +9935,10 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>94</v>
@@ -9825,16 +9959,16 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>538</v>
+        <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>282</v>
+        <v>523</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>283</v>
+        <v>554</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>284</v>
+        <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>84</v>
@@ -9842,10 +9976,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9856,7 +9990,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>84</v>
@@ -9868,20 +10002,18 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>376</v>
+        <v>556</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
       </c>
@@ -9929,13 +10061,13 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>84</v>
@@ -9953,27 +10085,27 @@
         <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>543</v>
+        <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>384</v>
+        <v>560</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>385</v>
+        <v>561</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9984,7 +10116,7 @@
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>84</v>
@@ -9993,23 +10125,21 @@
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>183</v>
+        <v>563</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
@@ -10033,13 +10163,13 @@
         <v>84</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>548</v>
+        <v>84</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>392</v>
+        <v>84</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -10057,16 +10187,16 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>549</v>
+        <v>84</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -10084,10 +10214,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>137</v>
+        <v>560</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>394</v>
+        <v>567</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10098,14 +10228,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10121,22 +10251,22 @@
         <v>84</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>183</v>
+        <v>503</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>397</v>
+        <v>569</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>398</v>
+        <v>570</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>399</v>
+        <v>571</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>400</v>
+        <v>572</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10161,13 +10291,13 @@
         <v>84</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>402</v>
+        <v>84</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10185,7 +10315,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10209,27 +10339,27 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>403</v>
+        <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>404</v>
+        <v>573</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>405</v>
+        <v>574</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>406</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10240,7 +10370,7 @@
         <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>84</v>
@@ -10252,20 +10382,16 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>552</v>
+        <v>162</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10313,47 +10439,941 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>551</v>
+        <v>164</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR65" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G66" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AI65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
+      <c r="H66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR66" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR67" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AQ65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR65" t="s" s="2">
+      <c r="AK68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AR68" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR69" t="s" s="2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR70" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR72" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR65">
+  <autoFilter ref="A1:AR72">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10363,7 +11383,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
+  <conditionalFormatting sqref="A2:AI71">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1476-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>1476-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
+    <t>http://va.gov/identifiers/$Sta3n/63.05</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1476-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
+    <t>1476-1: fixed value = http://va.gov/identifiers/$Sta3n/63.05</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
